--- a/data/trans_orig/IPAQ_MET-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IPAQ_MET-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2016</t>
+          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68232</t>
+          <t>68186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101959</t>
+          <t>102876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42060</t>
+          <t>40245</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92803</t>
+          <t>93833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135006</t>
+          <t>135962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295298</t>
+          <t>296892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>349050</t>
+          <t>350717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>359192</t>
+          <t>358841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420143</t>
+          <t>424817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>668714</t>
+          <t>674865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>755249</t>
+          <t>756963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>320183</t>
+          <t>321254</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>374509</t>
+          <t>374117</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>543546</t>
+          <t>538199</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>605679</t>
+          <t>604789</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>879251</t>
+          <t>876551</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>965021</t>
+          <t>959169</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>273888</t>
+          <t>271168</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>338237</t>
+          <t>336816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108448</t>
+          <t>108180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150120</t>
+          <t>152805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390551</t>
+          <t>392194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>472487</t>
+          <t>475662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1033428</t>
+          <t>1032937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1125225</t>
+          <t>1124524</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>941342</t>
+          <t>942699</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1029917</t>
+          <t>1032368</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1996328</t>
+          <t>1996189</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2124535</t>
+          <t>2139361</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>652589</t>
+          <t>649563</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>737216</t>
+          <t>736241</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>831026</t>
+          <t>824011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>919914</t>
+          <t>914508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1504399</t>
+          <t>1504981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1631191</t>
+          <t>1635595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67263</t>
+          <t>67844</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103892</t>
+          <t>103791</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>25667</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50949</t>
+          <t>50056</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100378</t>
+          <t>102221</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144735</t>
+          <t>144652</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>273229</t>
+          <t>271702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>324608</t>
+          <t>320340</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>303412</t>
+          <t>301638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>349221</t>
+          <t>348973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>590792</t>
+          <t>590446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>656130</t>
+          <t>657734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143559</t>
+          <t>143180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186261</t>
+          <t>188306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>166112</t>
+          <t>166608</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>212683</t>
+          <t>210607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322521</t>
+          <t>316743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>386094</t>
+          <t>381073</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>432862</t>
+          <t>434384</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>520114</t>
+          <t>516361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166368</t>
+          <t>166224</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>224014</t>
+          <t>220950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>620001</t>
+          <t>619115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>716875</t>
+          <t>718489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1640199</t>
+          <t>1644015</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1759941</t>
+          <t>1755473</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1642342</t>
+          <t>1643013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1768259</t>
+          <t>1771410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3321626</t>
+          <t>3324268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3482685</t>
+          <t>3496720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1152547</t>
+          <t>1153990</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1262301</t>
+          <t>1263017</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1567920</t>
+          <t>1572666</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1696694</t>
+          <t>1697484</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2756821</t>
+          <t>2750413</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2918565</t>
+          <t>2914371</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2023</t>
+          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62249</t>
+          <t>62259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92703</t>
+          <t>95230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53454</t>
+          <t>53047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77227</t>
+          <t>76964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>122702</t>
+          <t>121526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160943</t>
+          <t>159796</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189669</t>
+          <t>188576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231037</t>
+          <t>230518</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236439</t>
+          <t>237898</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277586</t>
+          <t>279287</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>438495</t>
+          <t>438833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>497216</t>
+          <t>497502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>207611</t>
+          <t>208577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>250681</t>
+          <t>249545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>414266</t>
+          <t>411609</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>454440</t>
+          <t>453311</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>632031</t>
+          <t>632298</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>692345</t>
+          <t>693738</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,61%</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3242,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402502</t>
+          <t>393269</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>672153</t>
+          <t>666767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>384489</t>
+          <t>386033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1020732</t>
+          <t>979728</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945678</t>
+          <t>926144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1657463</t>
+          <t>1685251</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1005945</t>
+          <t>1015258</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1520346</t>
+          <t>1536027</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>712540</t>
+          <t>670971</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1068482</t>
+          <t>1069617</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1856947</t>
+          <t>1867007</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2489113</t>
+          <t>2547231</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3440,12 +3440,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>56,25%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>366868</t>
+          <t>374725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>627734</t>
+          <t>632958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>535575</t>
+          <t>542583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>869179</t>
+          <t>859686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1033412</t>
+          <t>1028277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1443670</t>
+          <t>1457641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>183526</t>
+          <t>182979</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>233648</t>
+          <t>232521</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3713,12 +3713,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143780</t>
+          <t>144454</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184560</t>
+          <t>182827</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3748,12 +3748,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>338152</t>
+          <t>336805</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>406951</t>
+          <t>400909</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -3811,12 +3811,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>302471</t>
+          <t>301256</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>356525</t>
+          <t>356989</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>316283</t>
+          <t>318344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>364254</t>
+          <t>363038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>635587</t>
+          <t>637325</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>708459</t>
+          <t>708024</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,17%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90819</t>
+          <t>91638</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130412</t>
+          <t>132328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137633</t>
+          <t>137528</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175160</t>
+          <t>174423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239115</t>
+          <t>241537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>297133</t>
+          <t>297464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>675151</t>
+          <t>684684</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>953664</t>
+          <t>947856</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>608067</t>
+          <t>610905</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1337549</t>
+          <t>1316164</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1434476</t>
+          <t>1442406</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2190794</t>
+          <t>2189212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -4267,12 +4267,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1549985</t>
+          <t>1553751</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2087430</t>
+          <t>2098244</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1242295</t>
+          <t>1255042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1665821</t>
+          <t>1670803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2974309</t>
+          <t>2967011</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3680549</t>
+          <t>3681767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>680718</t>
+          <t>685015</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>974880</t>
+          <t>974293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1080401</t>
+          <t>1082494</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1452382</t>
+          <t>1453690</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1920646</t>
+          <t>1890844</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2391222</t>
+          <t>2379337</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IPAQ_MET-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IPAQ_MET-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68186</t>
+          <t>68555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102876</t>
+          <t>101871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>19951</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40245</t>
+          <t>41893</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93833</t>
+          <t>94260</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135962</t>
+          <t>135030</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>296892</t>
+          <t>294829</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>350717</t>
+          <t>347500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>358841</t>
+          <t>359164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>424817</t>
+          <t>421169</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>674865</t>
+          <t>671614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>756963</t>
+          <t>754936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>321254</t>
+          <t>323061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>374117</t>
+          <t>377427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>538199</t>
+          <t>542538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>604789</t>
+          <t>605826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>876551</t>
+          <t>881959</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>959169</t>
+          <t>960971</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271168</t>
+          <t>271502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>336816</t>
+          <t>337952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108180</t>
+          <t>107807</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>152805</t>
+          <t>150440</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>392194</t>
+          <t>395902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>475662</t>
+          <t>472792</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1032937</t>
+          <t>1030902</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1124524</t>
+          <t>1128357</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>942699</t>
+          <t>944445</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1032368</t>
+          <t>1035110</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1996189</t>
+          <t>2004311</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2139361</t>
+          <t>2138386</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>649563</t>
+          <t>651320</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>736241</t>
+          <t>743651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>824011</t>
+          <t>826848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>914508</t>
+          <t>915655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1504981</t>
+          <t>1501540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1635595</t>
+          <t>1629913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67844</t>
+          <t>68604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103791</t>
+          <t>104618</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>25815</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50056</t>
+          <t>49286</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>102221</t>
+          <t>101541</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144652</t>
+          <t>144771</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>271702</t>
+          <t>272508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>320340</t>
+          <t>319940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>301638</t>
+          <t>301780</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>348973</t>
+          <t>347665</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>590446</t>
+          <t>589088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>657734</t>
+          <t>657339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143180</t>
+          <t>143099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188306</t>
+          <t>188385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>166608</t>
+          <t>167004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210607</t>
+          <t>214698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>316743</t>
+          <t>320487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381073</t>
+          <t>385920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>434384</t>
+          <t>431126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>516361</t>
+          <t>515224</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166224</t>
+          <t>165954</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220950</t>
+          <t>220992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>619115</t>
+          <t>615669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>718489</t>
+          <t>717102</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1644015</t>
+          <t>1645004</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1755473</t>
+          <t>1760507</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1643013</t>
+          <t>1646147</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1771410</t>
+          <t>1765393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3324268</t>
+          <t>3314402</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3496720</t>
+          <t>3484304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1153990</t>
+          <t>1145662</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1263017</t>
+          <t>1259287</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1572666</t>
+          <t>1576840</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1697484</t>
+          <t>1693095</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2750413</t>
+          <t>2757953</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2914371</t>
+          <t>2925057</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -2781,32 +2781,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>80623</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62259</t>
+          <t>65615</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95230</t>
+          <t>99093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2816,17 +2816,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>64395</t>
+          <t>70026</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53047</t>
+          <t>58416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76964</t>
+          <t>84561</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2851,32 +2851,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>140820</t>
+          <t>150649</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121526</t>
+          <t>130949</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159796</t>
+          <t>172940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -2894,32 +2894,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>210408</t>
+          <t>241152</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>188576</t>
+          <t>217653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230518</t>
+          <t>264291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2929,32 +2929,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>256968</t>
+          <t>280891</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>237898</t>
+          <t>258284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279287</t>
+          <t>301820</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2964,32 +2964,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>467376</t>
+          <t>522043</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>438833</t>
+          <t>490106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>497502</t>
+          <t>552280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -3007,32 +3007,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>228104</t>
+          <t>256754</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>208577</t>
+          <t>234755</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>249545</t>
+          <t>281405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3042,32 +3042,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>434145</t>
+          <t>471122</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>411609</t>
+          <t>448326</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>453311</t>
+          <t>492831</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3077,32 +3077,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>662249</t>
+          <t>727875</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>632298</t>
+          <t>695252</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>693738</t>
+          <t>762186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -3120,17 +3120,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3155,17 +3155,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3190,17 +3190,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3237,32 +3237,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>577877</t>
+          <t>632586</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393269</t>
+          <t>576235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>666767</t>
+          <t>678712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3272,32 +3272,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>567649</t>
+          <t>407119</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>386033</t>
+          <t>376085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>979728</t>
+          <t>444410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3307,32 +3307,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1145526</t>
+          <t>1039705</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926144</t>
+          <t>985821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1685251</t>
+          <t>1104322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -3350,32 +3350,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1166142</t>
+          <t>1009383</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1015258</t>
+          <t>954759</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1536027</t>
+          <t>1062354</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3385,32 +3385,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>946194</t>
+          <t>1061352</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>670971</t>
+          <t>1013726</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1069617</t>
+          <t>1106751</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3420,32 +3420,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2112336</t>
+          <t>2070735</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1867007</t>
+          <t>1996506</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2547231</t>
+          <t>2140024</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -3463,32 +3463,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>546308</t>
+          <t>588597</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>374725</t>
+          <t>537111</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>632958</t>
+          <t>634525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3498,32 +3498,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>723980</t>
+          <t>702921</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>542583</t>
+          <t>662336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>859686</t>
+          <t>747263</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3533,32 +3533,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1270288</t>
+          <t>1291519</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1028277</t>
+          <t>1231279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1457641</t>
+          <t>1356881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -3576,17 +3576,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3646,17 +3646,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3693,102 +3693,102 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>207021</t>
+          <t>239373</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>182979</t>
+          <t>214377</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>232521</t>
+          <t>268073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>33,64%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>37,67%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>179110</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>157442</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>198965</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>24,37%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>27,07%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>418483</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>389944</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>463190</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>28,93%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>26,96%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>32,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>35,96%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>163703</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>144454</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>182827</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>24,79%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>370724</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>336805</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>400909</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>28,36%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -3806,32 +3806,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>329036</t>
+          <t>348805</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>301256</t>
+          <t>317727</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>356989</t>
+          <t>374828</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3841,32 +3841,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>341033</t>
+          <t>383296</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>318344</t>
+          <t>359701</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>363038</t>
+          <t>407453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3876,32 +3876,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>670068</t>
+          <t>732101</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>637325</t>
+          <t>696931</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>768891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -3919,102 +3919,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>110566</t>
+          <t>123409</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91638</t>
+          <t>101584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>132328</t>
+          <t>146536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>172471</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>154233</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>194333</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>23,47%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>20,99%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>26,44%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>295881</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>263338</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>323205</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>20,46%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>155728</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>137528</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>174423</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>26,41%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>266294</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>241537</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>297464</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>20,37%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -4032,17 +4032,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4067,17 +4067,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4102,17 +4102,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4149,32 +4149,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>861324</t>
+          <t>952582</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>684684</t>
+          <t>889768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>947856</t>
+          <t>1019997</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4184,32 +4184,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>795746</t>
+          <t>656255</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>610905</t>
+          <t>618104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1316164</t>
+          <t>702225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4219,32 +4219,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1657070</t>
+          <t>1608837</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1442406</t>
+          <t>1538555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2189212</t>
+          <t>1687373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -4262,32 +4262,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1705586</t>
+          <t>1599340</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1553751</t>
+          <t>1532609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2098244</t>
+          <t>1661749</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4297,32 +4297,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1544195</t>
+          <t>1725538</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1255042</t>
+          <t>1677338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1670803</t>
+          <t>1783426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4332,32 +4332,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3249781</t>
+          <t>3324878</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2967011</t>
+          <t>3238984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3681767</t>
+          <t>3404736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -4375,32 +4375,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>884979</t>
+          <t>968761</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>685015</t>
+          <t>909135</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>974293</t>
+          <t>1024759</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4410,32 +4410,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1313853</t>
+          <t>1346514</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1082494</t>
+          <t>1293531</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1453690</t>
+          <t>1396895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4445,32 +4445,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2198832</t>
+          <t>2315275</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1890844</t>
+          <t>2238893</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2379337</t>
+          <t>2393086</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -4488,17 +4488,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4523,17 +4523,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
